--- a/OIC DOCS/auto_oic_assessment_1.xlsx
+++ b/OIC DOCS/auto_oic_assessment_1.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Labour Charge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quter Panel LH</t>
+          <t>aaa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8729</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Labour Charge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rear Bumper</t>
+          <t>bbb</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8729</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Labour Charge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fender RH</t>
+          <t>ccc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -754,690 +754,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>fut Door RH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>8570</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rear Door RH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>9110</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Glass</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Quter Panel RH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8861</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Glass</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Side minor RH</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2270</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Side mirror LH</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2270</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>feet Bumper Bubt</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Glass</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Flood</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Carbone Cheye Accedator</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>UNIT HEAD LAMP LH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>jumper</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Metallic Parts</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>bbb</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ccc</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Metallic Parts</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Claim number</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>35010231260389998592</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>35010231260389998592</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Labour Charge</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>aaa</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>8729</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Labour Charge</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>bbb</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>8729</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Labour Charge</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>ccc</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>8729</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Labour Charge</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Claim number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>70020462520779997184</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
         <is>
           <t>8729</t>
         </is>
